--- a/MARGIN30_2010.xlsx
+++ b/MARGIN30_2010.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа ≥30%" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа ≥29%" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Лоты с маржой ≥30% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 15</t>
+          <t>Лоты с маржой ≥29% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1583,66 +1583,70 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>0325300007726000124</t>
+          <t>0345100011326000005</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>496200</v>
+        <v>814065.0699999999</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>300000</v>
+        <v>575000</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.3954050785973398</v>
+        <v>0.294</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>50413.31835616439</v>
+        <v>78638</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3704919206562006</v>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr"/>
+        <v>0.2646</v>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
+        </is>
+      </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1652,93 +1656,162 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>26.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0325300007726000124</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>44-ФЗ · запрос котировок</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Росэлторг</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>496200</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>0.3954050785973398</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>50413.31835616439</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>0.3704919206562006</v>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>http://roseltorg.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>21.10.2026 13:00</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>588439</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с пере…</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Электронная торговая площадка ONLINECONTRACT</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H19" s="7" t="n">
         <v>203056.8</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I19" s="7" t="n">
         <v>129000</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="J19" s="8" t="n">
         <v>0.365</v>
       </c>
-      <c r="K18" s="8" t="n">
+      <c r="K19" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L19" s="7" t="n">
         <v>40841</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M19" s="8" t="n">
         <v>0.339</v>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>оценка (низкая)</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="12" t="inlineStr"/>
-      <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="12" t="inlineStr"/>
+      <c r="C20" s="12" t="inlineStr"/>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr"/>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="13" t="n">
-        <v>121903926.65</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>61710833</v>
-      </c>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="13" t="n">
-        <v>31570403.29042266</v>
-      </c>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr"/>
+      <c r="G20" s="12" t="inlineStr"/>
+      <c r="H20" s="13" t="n">
+        <v>122717991.72</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>62285833</v>
+      </c>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="13" t="n">
+        <v>31649041.29042266</v>
+      </c>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1768,6 +1841,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/MARGIN30_2010.xlsx
+++ b/MARGIN30_2010.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа ≥29%" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа ≥25%" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Лоты с маржой ≥29% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 16</t>
+          <t>Лоты с маржой ≥25% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1441,70 +1441,70 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 08:00</t>
+          <t>23.10.2026 06:00</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>0372200263426001564</t>
+          <t>32616477173</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>СПб ГБУЗ «Городская Александровская больница»</t>
+          <t>ГУП Свердловской обл. «Газовые Сети»</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 50 000 шт</t>
+          <t>Поставка изолирующих соединений для нужд Алапаевского ГУ в рамках программы догазификации</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>863700</v>
+        <v>1078709.42</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>500000</v>
+        <v>796671</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.421095287715642</v>
+        <v>0.261</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>107231.277260274</v>
+        <v>119178</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3972407298630055</v>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
+        <v>0.231</v>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
+          <t>изолирующие соединения — нужна спецификация</t>
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477173</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>https://etpgpb.ru/</t>
+          <t>http://utp.sberbank-ast.ru/Trade/NBT/PurchaseView/22/0/0/4259114</t>
         </is>
       </c>
     </row>
@@ -1514,66 +1514,70 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 09:00</t>
+          <t>23.10.2026 08:00</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>0372200014026000180</t>
+          <t>0372200263426001564</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
+          <t>СПб ГБУЗ «Городская Александровская больница»</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
+          <t>Пробирки вакуумные, 50 000 шт</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>352333.33</v>
+        <v>863700</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>178000</v>
+        <v>500000</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.495</v>
+        <v>0.421095287715642</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>96250</v>
+        <v>107231.277260274</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr"/>
+        <v>0.3972407298630055</v>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
+        </is>
+      </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>https://www.fabrikant.ru</t>
+          <t>https://etpgpb.ru/</t>
         </is>
       </c>
     </row>
@@ -1583,22 +1587,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>23.10.2026 09:00</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>0345100011326000005</t>
+          <t>0372200014026000180</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
+          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
+          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1608,45 +1612,41 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>814065.0699999999</v>
+        <v>352333.33</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>575000</v>
+        <v>178000</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.294</v>
+        <v>0.495</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>0.15</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>78638</v>
+        <v>96250</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.2646</v>
+        <v>0.474</v>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
-        </is>
-      </c>
+      <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>https://www.fabrikant.ru</t>
         </is>
       </c>
     </row>
@@ -1656,66 +1656,70 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>22.10.2026 10:00</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>0325300007726000124</t>
+          <t>32616472923</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+          <t>СПБ государственное автономное Стационарное учреждение Соци…</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+          <t>Поставка осветительных электрических товаров, кабеля и регулятора жидкости.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>496200</v>
+        <v>914481.61</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>300000</v>
+        <v>685861</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.3954050785973398</v>
+        <v>0.25</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>50413.31835616439</v>
+        <v>91833</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3704919206562006</v>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr"/>
+        <v>21.9</v>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>лампы, светильники, провод — характеристики не получены</t>
+        </is>
+      </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616472923</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>https://corp.roseltorg.ru/#notice/836386</t>
         </is>
       </c>
     </row>
@@ -1725,93 +1729,519 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>26.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0345100011326000005</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>814065.0699999999</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>575000</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>78638</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>http://www.rts-tender.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>20.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>32616450774</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>МУП «Уфимские инженерные сети» (банкрот)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Отводы в ППУ-ПЭ, 9 шт</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>223-ФЗ · запрос котировок</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>РЭСТ</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>639848.52</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>478894</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>0.2515509764717436</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>65125.55362472334</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>0.2207101141456235</v>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>СЕГОДНЯ до 10:00 МСК; заказчик в конкурсном производстве — отгрузка только после аванса 50%</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616450774</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q27nr7kub1j7074</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>22.10.2026 09:41</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0348100043326000102</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУЗ «Медико-санитарная часть № 152 Федеральног…</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Поставка медицинский изделий лот 2</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1065306.62</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>798980</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>62066</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>лапароскопический инструмент; нацрежим — российские (Эндомедиум, ЭлМед), цены по запросу</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0348100043326000102</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>http://www.rts-tender.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>26.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0325300007726000124</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>44-ФЗ · запрос котировок</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Росэлторг</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>496200</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>0.3954050785973398</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>50413.31835616439</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>0.3704919206562006</v>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>http://roseltorg.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>22.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>10762184</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Малые закупки · Малая закупка</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>443486.33</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>329310</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>47437</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>малая закупка СИЗ — позиции неизвестны</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>21.10.2026 13:00</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>588439</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с пере…</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Электронная торговая площадка ONLINECONTRACT</t>
         </is>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H24" s="7" t="n">
         <v>203056.8</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I24" s="7" t="n">
         <v>129000</v>
       </c>
-      <c r="J19" s="8" t="n">
+      <c r="J24" s="8" t="n">
         <v>0.365</v>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="K24" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L24" s="7" t="n">
         <v>40841</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M24" s="8" t="n">
         <v>0.339</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>оценка (низкая)</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>26.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>32616477523</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>АО «Коми Тепловая Компания»</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>223-ФЗ · Закупка иного способа размещен…</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>РТС-тендер</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>210371.75</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>157779</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>21126</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>0.2191</v>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>видеонаблюдение — нужна спецификация</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="12" t="inlineStr"/>
+      <c r="B26" s="12" t="inlineStr"/>
+      <c r="C26" s="12" t="inlineStr"/>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr"/>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr"/>
-      <c r="H20" s="13" t="n">
-        <v>122717991.72</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>62285833</v>
-      </c>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="14" t="n"/>
-      <c r="L20" s="13" t="n">
-        <v>31649041.29042266</v>
-      </c>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr"/>
+      <c r="H26" s="13" t="n">
+        <v>127070195.97</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>65533328</v>
+      </c>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="13" t="n">
+        <v>32055806.84404738</v>
+      </c>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1843,6 +2273,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/MARGIN30_2010.xlsx
+++ b/MARGIN30_2010.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Лоты с маржой ≥25% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 22</t>
+          <t>Лоты с маржой ≥25% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Форменная одежда службы безопасности</t>
+          <t>Форменная одежда СБ: 8 позиций, 145 комплектов (по ТЗ)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -836,32 +836,32 @@
         <v>4169750</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2818752</v>
+        <v>2925900</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.3239997601774687</v>
+        <v>0.2983032555908628</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>689630.0761643836</v>
+        <v>595560.0032876713</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.2961442487486347</v>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>оценка — нужна спецификация</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr"/>
+        <v>0.2693888846601725</v>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
+        </is>
+      </c>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
-        </is>
-      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -869,66 +869,70 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>22.10.2026 10:00</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>32616453117</t>
+          <t>0373200011426001679</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ГУП РБ «Салаватводоканал»</t>
+          <t>ГБУЗ г. Москвы «Городская Клиническая Больница № 67 Имени Л…</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Спецодежда зимняя, КЩС, сварщика, сигнальная (11 позиций)</t>
+          <t>Поставка контейнеров с поршнем для мочи (заявка 428-зк, лот 3)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос предложений (МСП)</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (corp)</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1500000</v>
+        <v>2389196.8</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>681523</v>
+        <v>1182360</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.5456513333333333</v>
+        <v>0.505</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>539980.1497260274</v>
+        <v>472881</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5269292771394903</v>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr"/>
+        <v>0.485</v>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>нужен российский поставщик контейнеров с поршнем ~12 ₽ (импорт ограничен)</t>
+        </is>
+      </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616453117</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0373200011426001679</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/835021</t>
+          <t>http://roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -938,65 +942,65 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 10:00</t>
+          <t>23.10.2026 04:00</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0373200011426001679</t>
+          <t>0338200002226000430</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ г. Москвы «Городская Клиническая Больница № 67 Имени Л…</t>
+          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Поставка контейнеров с поршнем для мочи (заявка 428-зк, лот 3)</t>
+          <t>Пробирки вакуумные, 82 200 шт</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>2389196.8</v>
+        <v>2221608</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1182360</v>
+        <v>1114900</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.505</v>
+        <v>0.4981562903986662</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>472881</v>
+        <v>426123.7896109588</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
+        <v>0.4774771362138123</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>нужен российский поставщик контейнеров с поршнем ~12 ₽ (импорт ограничен)</t>
+          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0373200011426001679</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
@@ -1011,70 +1015,66 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 04:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>0338200002226000430</t>
+          <t>32616480814</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
+          <t>АО «Петербургский нефтяной терминал»</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 82 200 шт</t>
+          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · конкурентный отбор</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>ZakazRF (АГЗРТ)</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2221608</v>
+        <v>3163250.24</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1114900</v>
+        <v>2107397</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.4981562903986662</v>
+        <v>0.3337874527435427</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>426123.7896109588</v>
+        <v>416985.6198210191</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4774771362138123</v>
+        <v>0.3063352565298155</v>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
           <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
-        </is>
-      </c>
+      <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
         </is>
       </c>
     </row>
@@ -1084,66 +1084,70 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>22.10.2026 15:00</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>32616480814</t>
+          <t>32616465624</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>АО «Петербургский нефтяной терминал»</t>
+          <t>ООО «Управление по Подготовке Технологической Жидкости Для …</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
+          <t>Поставка запорной арматуры для нужд ООО "УПТЖ для ППД" (4638856)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · конкурентный отбор</t>
+          <t>223-ФЗ · Закупка иного способа размещен…</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>ZakazRF (АГЗРТ)</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>3163250.24</v>
+        <v>1719646.12</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>2107397</v>
+        <v>1096000</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.3337874527435427</v>
+        <v>0.363</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>416985.6198210191</v>
+        <v>342777</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.3063352565298155</v>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr"/>
+        <v>0.336</v>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>17 типов затворов, цен за единицу нет — себес оценочный</t>
+        </is>
+      </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616465624</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
+          <t>http://www.b2b-center.ru/market/postavka-zapornoi-armatury-dlia-nuzhd-ooo-uptzh-dlia-ppd/tender-4638856/</t>
         </is>
       </c>
     </row>
@@ -1153,70 +1157,66 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 15:00</t>
+          <t>22.10.2026 05:00</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>32616465624</t>
+          <t>32616484297</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ООО «Управление по Подготовке Технологической Жидкости Для …</t>
+          <t>МАУ ДО ДМЦ «Алый парус», Тюменская обл.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Поставка запорной арматуры для нужд ООО "УПТЖ для ППД" (4638856)</t>
+          <t>Костюм «Горка-3» летний, палатка, 121 шт</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа размещен…</t>
+          <t>223-ФЗ · электронный магазин</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>РТС-тендер 223</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1719646.12</v>
+        <v>671066</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1096000</v>
+        <v>399300</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.363</v>
+        <v>0.4049765596826541</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>342777</v>
+        <v>158695.0455320548</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>17 типов затворов, цен за единицу нет — себес оценочный</t>
-        </is>
-      </c>
+        <v>0.3804578076678099</v>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616465624</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484297</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>http://www.b2b-center.ru/market/postavka-zapornoi-armatury-dlia-nuzhd-ooo-uptzh-dlia-ppd/tender-4638856/</t>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4067536</t>
         </is>
       </c>
     </row>
@@ -1226,66 +1226,70 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 05:00</t>
+          <t>23.10.2026 10:00</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>32616484297</t>
+          <t>0318300596226000122</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>МАУ ДО ДМЦ «Алый парус», Тюменская обл.</t>
+          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства З…</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Костюм «Горка-3» летний, палатка, 121 шт</t>
+          <t>Поставка медицинских изделий (пробирки для забора крови)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · электронный магазин</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер 223</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>671066</v>
+        <v>600000</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>399300</v>
+        <v>269792</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.4049765596826541</v>
+        <v>0.55</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>158695.0455320548</v>
+        <v>142577</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.3804578076678099</v>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr"/>
+        <v>0.532</v>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>количество не задано (цены за ед.); проверить крышку с двухэтапным снятием у МиниМед</t>
+        </is>
+      </c>
       <c r="P12" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484297</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318300596226000122</t>
         </is>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4067536</t>
+          <t>https://www.fabrikant.ru</t>
         </is>
       </c>
     </row>
@@ -1295,22 +1299,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 10:00</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>0318300596226000122</t>
+          <t>0318200081326000039</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства З…</t>
+          <t>ГБУЗ «Бюро судебно-медицинской экспертизы № 2» министерства…</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Поставка медицинских изделий (пробирки для забора крови)</t>
+          <t>Поставка изделий медицинского назначения (контейнеров для сбора проб)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1320,26 +1324,26 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>600000</v>
+        <v>247273</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>269792</v>
+        <v>40900</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.55</v>
+        <v>0.835</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>142577</v>
+        <v>120467</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.532</v>
+        <v>0.828</v>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
@@ -1348,17 +1352,17 @@
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>количество не задано (цены за ед.); проверить крышку с двухэтапным снятием у МиниМед</t>
+          <t>цены заказчика 39–58 ₽ при рынке 5–10 ₽ — ожидать демпинг</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318300596226000122</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318200081326000039</t>
         </is>
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>https://www.fabrikant.ru</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1368,70 +1372,70 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>23.10.2026 06:00</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>0318200081326000039</t>
+          <t>32616477173</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Бюро судебно-медицинской экспертизы № 2» министерства…</t>
+          <t>ГУП Свердловской обл. «Газовые Сети»</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Поставка изделий медицинского назначения (контейнеров для сбора проб)</t>
+          <t>Поставка изолирующих соединений для нужд Алапаевского ГУ в рамках программы догазификации</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>247273</v>
+        <v>1078709.42</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>40900</v>
+        <v>796671</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.835</v>
+        <v>0.261</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>120467</v>
+        <v>119178</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.828</v>
+        <v>0.231</v>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>цены заказчика 39–58 ₽ при рынке 5–10 ₽ — ожидать демпинг</t>
+          <t>изолирующие соединения — нужна спецификация</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318200081326000039</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477173</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>http://utp.sberbank-ast.ru/Trade/NBT/PurchaseView/22/0/0/4259114</t>
         </is>
       </c>
     </row>
@@ -1441,70 +1445,70 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 06:00</t>
+          <t>23.10.2026 08:00</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>32616477173</t>
+          <t>0372200263426001564</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ГУП Свердловской обл. «Газовые Сети»</t>
+          <t>СПб ГБУЗ «Городская Александровская больница»</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Поставка изолирующих соединений для нужд Алапаевского ГУ в рамках программы догазификации</t>
+          <t>Пробирки вакуумные, 50 000 шт</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной…</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1078709.42</v>
+        <v>863700</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>796671</v>
+        <v>500000</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.261</v>
+        <v>0.421095287715642</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>119178</v>
+        <v>107231.277260274</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
+        <v>0.3972407298630055</v>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>изолирующие соединения — нужна спецификация</t>
+          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477173</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>http://utp.sberbank-ast.ru/Trade/NBT/PurchaseView/22/0/0/4259114</t>
+          <t>https://etpgpb.ru/</t>
         </is>
       </c>
     </row>
@@ -1514,70 +1518,66 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 08:00</t>
+          <t>23.10.2026 09:00</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>0372200263426001564</t>
+          <t>0372200014026000180</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>СПб ГБУЗ «Городская Александровская больница»</t>
+          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 50 000 шт</t>
+          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>863700</v>
+        <v>352333.33</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>500000</v>
+        <v>178000</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.421095287715642</v>
+        <v>0.495</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>107231.277260274</v>
+        <v>96250</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3972407298630055</v>
-      </c>
-      <c r="N16" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
-        </is>
-      </c>
+        <v>0.474</v>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>https://etpgpb.ru/</t>
+          <t>https://www.fabrikant.ru</t>
         </is>
       </c>
     </row>
@@ -1587,66 +1587,70 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 09:00</t>
+          <t>22.10.2026 10:00</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>0372200014026000180</t>
+          <t>32616472923</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
+          <t>СПБ государственное автономное Стационарное учреждение Соци…</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
+          <t>Поставка осветительных электрических товаров, кабеля и регулятора жидкости.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>352333.33</v>
+        <v>914481.61</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>178000</v>
+        <v>685861</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.495</v>
+        <v>0.25</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>96250</v>
+        <v>91833</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.474</v>
+        <v>21.9</v>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr"/>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>лампы, светильники, провод — характеристики не получены</t>
+        </is>
+      </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616472923</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>https://www.fabrikant.ru</t>
+          <t>https://corp.roseltorg.ru/#notice/836386</t>
         </is>
       </c>
     </row>
@@ -1656,70 +1660,70 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 10:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>32616472923</t>
+          <t>0345100011326000005</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>СПБ государственное автономное Стационарное учреждение Соци…</t>
+          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Поставка осветительных электрических товаров, кабеля и регулятора жидкости.</t>
+          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной…</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>914481.61</v>
+        <v>814065.0699999999</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>685861</v>
+        <v>575000</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>91833</v>
+        <v>78638</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>21.9</v>
+        <v>0.2646</v>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>оценка (низкая)</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>лампы, светильники, провод — характеристики не получены</t>
+          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616472923</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/836386</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1729,70 +1733,70 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>20.10.2026 10:00</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>0345100011326000005</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
+          <t>МУП «Уфимские инженерные сети» (банкрот)</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
+          <t>Отводы в ППУ-ПЭ, 9 шт</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>РЭСТ</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>814065.0699999999</v>
+        <v>639848.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>575000</v>
+        <v>478894</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.294</v>
+        <v>0.2515509764717436</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>78638</v>
+        <v>65125.55362472334</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2646</v>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>средняя</t>
+        <v>0.2207101141456235</v>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
+          <t>СЕГОДНЯ до 10:00 МСК; заказчик в конкурсном производстве — отгрузка только после аванса 50%</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616450774</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q27nr7kub1j7074</t>
         </is>
       </c>
     </row>
@@ -1802,70 +1806,70 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>20.10.2026 10:00</t>
+          <t>22.10.2026 09:41</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>32616450774</t>
+          <t>0348100043326000102</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>МУП «Уфимские инженерные сети» (банкрот)</t>
+          <t>Федеральное ГБУЗ «Медико-санитарная часть № 152 Федеральног…</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Отводы в ППУ-ПЭ, 9 шт</t>
+          <t>Поставка медицинский изделий лот 2</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос котировок</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>РЭСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>639848.52</v>
+        <v>1065306.62</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>478894</v>
+        <v>798980</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.2515509764717436</v>
+        <v>0.25</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>65125.55362472334</v>
+        <v>62066</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2207101141456235</v>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
+        <v>21.9</v>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>СЕГОДНЯ до 10:00 МСК; заказчик в конкурсном производстве — отгрузка только после аванса 50%</t>
+          <t>лапароскопический инструмент; нацрежим — российские (Эндомедиум, ЭлМед), цены по запросу</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616450774</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0348100043326000102</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q27nr7kub1j7074</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1875,70 +1879,66 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 09:41</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>0348100043326000102</t>
+          <t>0325300007726000124</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Федеральное ГБУЗ «Медико-санитарная часть № 152 Федеральног…</t>
+          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Поставка медицинский изделий лот 2</t>
+          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1065306.62</v>
+        <v>496200</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>798980</v>
+        <v>300000</v>
       </c>
       <c r="J21" s="8" t="n">
+        <v>0.3954050785973398</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <v>0.15</v>
-      </c>
       <c r="L21" s="7" t="n">
-        <v>62066</v>
+        <v>50413.31835616439</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>лапароскопический инструмент; нацрежим — российские (Эндомедиум, ЭлМед), цены по запросу</t>
-        </is>
-      </c>
+        <v>0.3704919206562006</v>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0348100043326000102</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>http://roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -1948,68 +1948,64 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>22.10.2026 08:00</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>0325300007726000124</t>
+          <t>10762184</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>496200</v>
+        <v>443486.33</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>300000</v>
+        <v>329310</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.3954050785973398</v>
+        <v>0.257</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>50413.31835616439</v>
+        <v>47437</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3704919206562006</v>
-      </c>
-      <c r="N22" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
-        </is>
-      </c>
-      <c r="Q22" s="10" t="inlineStr">
-        <is>
-          <t>http://roseltorg.ru</t>
-        </is>
-      </c>
+        <v>0.227</v>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>малая закупка СИЗ — позиции неизвестны</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -2017,51 +2013,51 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 08:00</t>
+          <t>21.10.2026 13:00</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>10762184</t>
+          <t>588439</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
+          <t>ООО «Карсар»</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
+          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
+          <t>Коммерческие · Конкурентный лист с пере…</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Электронная торговая площадка ONLINECONTRACT</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>443486.33</v>
+        <v>203056.8</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>329310</v>
+        <v>129000</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.257</v>
+        <v>0.365</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>47437</v>
+        <v>40841</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.227</v>
+        <v>0.339</v>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
@@ -2070,7 +2066,7 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>малая закупка СИЗ — позиции неизвестны</t>
+          <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
         </is>
       </c>
       <c r="P23" s="5" t="inlineStr"/>
@@ -2082,51 +2078,51 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 13:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>588439</t>
+          <t>32616477523</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>ООО «Карсар»</t>
+          <t>АО «Коми Тепловая Компания»</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
+          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Коммерческие · Конкурентный лист с пере…</t>
+          <t>223-ФЗ · Закупка иного способа размещен…</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Электронная торговая площадка ONLINECONTRACT</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>203056.8</v>
+        <v>210371.75</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>129000</v>
+        <v>157779</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.365</v>
+        <v>0.25</v>
       </c>
       <c r="K24" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>40841</v>
+        <v>21126</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.339</v>
+        <v>0.2191</v>
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
@@ -2135,154 +2131,86 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
+          <t>видеонаблюдение — нужна спецификация</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>26.10.2026 10:00</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>32616477523</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>АО «Коми Тепловая Компания»</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>223-ФЗ · Закупка иного способа размещен…</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>РТС-тендер</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>210371.75</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>157779</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>21126</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>0.2191</v>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>видеонаблюдение — нужна спецификация</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr">
-        <is>
-          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="12" t="inlineStr"/>
-      <c r="B26" s="12" t="inlineStr"/>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr"/>
-      <c r="H26" s="13" t="n">
-        <v>127070195.97</v>
-      </c>
-      <c r="I26" s="13" t="n">
-        <v>65533328</v>
-      </c>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="13" t="n">
-        <v>32055806.84404738</v>
-      </c>
-      <c r="M26" s="14" t="n"/>
-      <c r="N26" s="14" t="n"/>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="14" t="n"/>
-      <c r="Q26" s="14" t="n"/>
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr"/>
+      <c r="H25" s="13" t="n">
+        <v>125570195.97</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>64958953</v>
+      </c>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="13" t="n">
+        <v>31421756.62144464</v>
+      </c>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/MARGIN30_2010.xlsx
+++ b/MARGIN30_2010.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Лоты с маржой ≥25% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 21</t>
+          <t>Лоты с маржой ≥25% при НМЦК — из 9 выгрузок 19.10, без аукционов, подача с 20.10. Всего 20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -804,64 +804,72 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>22.10.2026 10:00</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>B1510261835045</t>
+          <t>0373200011426001679</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт», Судак</t>
+          <t>ГБУЗ г. Москвы «Городская Клиническая Больница № 67 Имени Л…</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Форменная одежда СБ: 8 позиций, 145 комплектов (по ТЗ)</t>
+          <t>Поставка контейнеров с поршнем для мочи (заявка 428-зк, лот 3)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Коммерческий тендер</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (коммерч.)</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>4169750</v>
+        <v>2389196.8</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2925900</v>
+        <v>1182360</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.2983032555908628</v>
+        <v>0.505</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>595560.0032876713</v>
+        <v>472881</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.2693888846601725</v>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
+        <v>0.485</v>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
+          <t>нужен российский поставщик контейнеров с поршнем ~12 ₽ (импорт ограничен)</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0373200011426001679</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>http://roseltorg.ru</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -869,65 +877,65 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 10:00</t>
+          <t>23.10.2026 04:00</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0373200011426001679</t>
+          <t>0338200002226000430</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ г. Москвы «Городская Клиническая Больница № 67 Имени Л…</t>
+          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Поставка контейнеров с поршнем для мочи (заявка 428-зк, лот 3)</t>
+          <t>Пробирки вакуумные, 82 200 шт</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2389196.8</v>
+        <v>2221608</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1182360</v>
+        <v>1114900</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.505</v>
+        <v>0.4981562903986662</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>472881</v>
+        <v>426123.7896109588</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
+        <v>0.4774771362138123</v>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>нужен российский поставщик контейнеров с поршнем ~12 ₽ (импорт ограничен)</t>
+          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0373200011426001679</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
@@ -942,70 +950,66 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 04:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0338200002226000430</t>
+          <t>32616480814</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Камчатский краевой онкологический диспансер»</t>
+          <t>АО «Петербургский нефтяной терминал»</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 82 200 шт</t>
+          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>223-ФЗ · конкурентный отбор</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>ZakazRF (АГЗРТ)</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>2221608</v>
+        <v>3163250.24</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1114900</v>
+        <v>2107397</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.4981562903986662</v>
+        <v>0.3337874527435427</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>426123.7896109588</v>
+        <v>416985.6198210191</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.4774771362138123</v>
+        <v>0.3063352565298155</v>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
           <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>активатор посчитан с гелем (15 ₽) — с запасом; нужны РУ и реестр РФ (импорт запрещён)</t>
-        </is>
-      </c>
+      <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0338200002226000430</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>http://roseltorg.ru</t>
+          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
         </is>
       </c>
     </row>
@@ -1015,66 +1019,70 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>22.10.2026 15:00</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>32616480814</t>
+          <t>32616465624</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>АО «Петербургский нефтяной терминал»</t>
+          <t>ООО «Управление по Подготовке Технологической Жидкости Для …</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Задвижки 30с41нж/30с941нж, 70 шт</t>
+          <t>Поставка запорной арматуры для нужд ООО "УПТЖ для ППД" (4638856)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · конкурентный отбор</t>
+          <t>223-ФЗ · Закупка иного способа размещен…</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>ZakazRF (АГЗРТ)</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3163250.24</v>
+        <v>1719646.12</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2107397</v>
+        <v>1096000</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.3337874527435427</v>
+        <v>0.363</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>416985.6198210191</v>
+        <v>342777</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.3063352565298155</v>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr"/>
+        <v>0.336</v>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>17 типов затворов, цен за единицу нет — себес оценочный</t>
+        </is>
+      </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616480814</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616465624</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>https://223etp.zakazrf.ru/NotificationEX/id/509007</t>
+          <t>http://www.b2b-center.ru/market/postavka-zapornoi-armatury-dlia-nuzhd-ooo-uptzh-dlia-ppd/tender-4638856/</t>
         </is>
       </c>
     </row>
@@ -1084,70 +1092,66 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 15:00</t>
+          <t>22.10.2026 05:00</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>32616465624</t>
+          <t>32616484297</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ООО «Управление по Подготовке Технологической Жидкости Для …</t>
+          <t>МАУ ДО ДМЦ «Алый парус», Тюменская обл.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Поставка запорной арматуры для нужд ООО "УПТЖ для ППД" (4638856)</t>
+          <t>Костюм «Горка-3» летний, палатка, 121 шт</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа размещен…</t>
+          <t>223-ФЗ · электронный магазин</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>РТС-тендер 223</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1719646.12</v>
+        <v>671066</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1096000</v>
+        <v>399300</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.363</v>
+        <v>0.4049765596826541</v>
       </c>
       <c r="K10" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>342777</v>
+        <v>158695.0455320548</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>17 типов затворов, цен за единицу нет — себес оценочный</t>
-        </is>
-      </c>
+        <v>0.3804578076678099</v>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616465624</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484297</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>http://www.b2b-center.ru/market/postavka-zapornoi-armatury-dlia-nuzhd-ooo-uptzh-dlia-ppd/tender-4638856/</t>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4067536</t>
         </is>
       </c>
     </row>
@@ -1157,66 +1161,70 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 05:00</t>
+          <t>23.10.2026 10:00</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>32616484297</t>
+          <t>0318300596226000122</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>МАУ ДО ДМЦ «Алый парус», Тюменская обл.</t>
+          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства З…</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Костюм «Горка-3» летний, палатка, 121 шт</t>
+          <t>Поставка медицинских изделий (пробирки для забора крови)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · электронный магазин</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер 223</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>671066</v>
+        <v>600000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>399300</v>
+        <v>269792</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.4049765596826541</v>
+        <v>0.55</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>158695.0455320548</v>
+        <v>142577</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.3804578076678099</v>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr"/>
+        <v>0.532</v>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>количество не задано (цены за ед.); проверить крышку с двухэтапным снятием у МиниМед</t>
+        </is>
+      </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484297</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318300596226000122</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4067536</t>
+          <t>https://www.fabrikant.ru</t>
         </is>
       </c>
     </row>
@@ -1226,22 +1234,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 10:00</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0318300596226000122</t>
+          <t>0318200081326000039</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Городская Поликлиника № 4 Города Сочи» Министерства З…</t>
+          <t>ГБУЗ «Бюро судебно-медицинской экспертизы № 2» министерства…</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Поставка медицинских изделий (пробирки для забора крови)</t>
+          <t>Поставка изделий медицинского назначения (контейнеров для сбора проб)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1251,26 +1259,26 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>600000</v>
+        <v>247273</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>269792</v>
+        <v>40900</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.55</v>
+        <v>0.835</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>142577</v>
+        <v>120467</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.532</v>
+        <v>0.828</v>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
@@ -1279,17 +1287,17 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>количество не задано (цены за ед.); проверить крышку с двухэтапным снятием у МиниМед</t>
+          <t>цены заказчика 39–58 ₽ при рынке 5–10 ₽ — ожидать демпинг</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318300596226000122</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318200081326000039</t>
         </is>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>https://www.fabrikant.ru</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1299,70 +1307,70 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>23.10.2026 06:00</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>0318200081326000039</t>
+          <t>32616477173</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ «Бюро судебно-медицинской экспертизы № 2» министерства…</t>
+          <t>ГУП Свердловской обл. «Газовые Сети»</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Поставка изделий медицинского назначения (контейнеров для сбора проб)</t>
+          <t>Поставка изолирующих соединений для нужд Алапаевского ГУ в рамках программы догазификации</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>247273</v>
+        <v>1078709.42</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>40900</v>
+        <v>796671</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.835</v>
+        <v>0.261</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>120467</v>
+        <v>119178</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.828</v>
+        <v>0.231</v>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>цены заказчика 39–58 ₽ при рынке 5–10 ₽ — ожидать демпинг</t>
+          <t>изолирующие соединения — нужна спецификация</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0318200081326000039</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477173</t>
         </is>
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>http://utp.sberbank-ast.ru/Trade/NBT/PurchaseView/22/0/0/4259114</t>
         </is>
       </c>
     </row>
@@ -1372,70 +1380,70 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 06:00</t>
+          <t>23.10.2026 08:00</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>32616477173</t>
+          <t>0372200263426001564</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ГУП Свердловской обл. «Газовые Сети»</t>
+          <t>СПб ГБУЗ «Городская Александровская больница»</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Поставка изолирующих соединений для нужд Алапаевского ГУ в рамках программы догазификации</t>
+          <t>Пробирки вакуумные, 50 000 шт</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной…</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1078709.42</v>
+        <v>863700</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>796671</v>
+        <v>500000</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.261</v>
+        <v>0.421095287715642</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>119178</v>
+        <v>107231.277260274</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
+        <v>0.3972407298630055</v>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>изолирующие соединения — нужна спецификация</t>
+          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477173</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>http://utp.sberbank-ast.ru/Trade/NBT/PurchaseView/22/0/0/4259114</t>
+          <t>https://etpgpb.ru/</t>
         </is>
       </c>
     </row>
@@ -1445,70 +1453,66 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 08:00</t>
+          <t>23.10.2026 09:00</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>0372200263426001564</t>
+          <t>0372200014026000180</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>СПб ГБУЗ «Городская Александровская больница»</t>
+          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные, 50 000 шт</t>
+          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>863700</v>
+        <v>352333.33</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>500000</v>
+        <v>178000</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0.421095287715642</v>
+        <v>0.495</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>107231.277260274</v>
+        <v>96250</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3972407298630055</v>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>посчитано для активатора БЕЗ геля (10 ₽); если в ТЗ с гелем (15 ₽) — при −25% убыток ~29 тыс., подавать не ниже −20%</t>
-        </is>
-      </c>
+        <v>0.474</v>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200263426001564</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>https://etpgpb.ru/</t>
+          <t>https://www.fabrikant.ru</t>
         </is>
       </c>
     </row>
@@ -1518,66 +1522,70 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>23.10.2026 09:00</t>
+          <t>22.10.2026 10:00</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>0372200014026000180</t>
+          <t>32616472923</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>СПБ ГБУЗ «Городская поликлиника № 60 Пушкинского района»</t>
+          <t>СПБ государственное автономное Стационарное учреждение Соци…</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Поставка шкафа телекоммуникационного для нужд СПб ГБУЗ "Городская поликлиника №60 Пушкинс…</t>
+          <t>Поставка осветительных электрических товаров, кабеля и регулятора жидкости.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · Запрос котировок в электронной…</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>352333.33</v>
+        <v>914481.61</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>178000</v>
+        <v>685861</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.495</v>
+        <v>0.25</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>96250</v>
+        <v>91833</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.474</v>
+        <v>21.9</v>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr"/>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>лампы, светильники, провод — характеристики не получены</t>
+        </is>
+      </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0372200014026000180</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616472923</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>https://www.fabrikant.ru</t>
+          <t>https://corp.roseltorg.ru/#notice/836386</t>
         </is>
       </c>
     </row>
@@ -1587,70 +1595,70 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 10:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>32616472923</t>
+          <t>0345100011326000005</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>СПБ государственное автономное Стационарное учреждение Соци…</t>
+          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Поставка осветительных электрических товаров, кабеля и регулятора жидкости.</t>
+          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной…</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>914481.61</v>
+        <v>814065.0699999999</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>685861</v>
+        <v>575000</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>91833</v>
+        <v>78638</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>21.9</v>
+        <v>0.2646</v>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>оценка (низкая)</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>лампы, светильники, провод — характеристики не получены</t>
+          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616472923</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>https://corp.roseltorg.ru/#notice/836386</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1660,70 +1668,70 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>20.10.2026 10:00</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>0345100011326000005</t>
+          <t>32616450774</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Федеральное казенное учреждение «Исправительная Колония № 4…</t>
+          <t>МУП «Уфимские инженерные сети» (банкрот)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Поставка оборудования для видеонаблюдения производственной зоны учреждения в целях обеспе…</t>
+          <t>Отводы в ППУ-ПЭ, 9 шт</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>223-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>РЭСТ</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>814065.0699999999</v>
+        <v>639848.52</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>575000</v>
+        <v>478894</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.294</v>
+        <v>0.2515509764717436</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>78638</v>
+        <v>65125.55362472334</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.2646</v>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>средняя</t>
+        <v>0.2207101141456235</v>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>ловушка ТЗ: диски ≥10 ТБ и ≥1000 МБ/с — подходит только SSD, он дороже НМЦК; камеры TRASSIR (реестр РФ)</t>
+          <t>СЕГОДНЯ до 10:00 МСК; заказчик в конкурсном производстве — отгрузка только после аванса 50%</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0345100011326000005</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616450774</t>
         </is>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q27nr7kub1j7074</t>
         </is>
       </c>
     </row>
@@ -1733,70 +1741,70 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>20.10.2026 10:00</t>
+          <t>22.10.2026 09:41</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>32616450774</t>
+          <t>0348100043326000102</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>МУП «Уфимские инженерные сети» (банкрот)</t>
+          <t>Федеральное ГБУЗ «Медико-санитарная часть № 152 Федеральног…</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Отводы в ППУ-ПЭ, 9 шт</t>
+          <t>Поставка медицинский изделий лот 2</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>223-ФЗ · запрос котировок</t>
+          <t>44-ФЗ · Запрос котировок в электронной …</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>РЭСТ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>639848.52</v>
+        <v>1065306.62</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>478894</v>
+        <v>798980</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.2515509764717436</v>
+        <v>0.25</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>65125.55362472334</v>
+        <v>62066</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2207101141456235</v>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
+        <v>21.9</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>СЕГОДНЯ до 10:00 МСК; заказчик в конкурсном производстве — отгрузка только после аванса 50%</t>
+          <t>лапароскопический инструмент; нацрежим — российские (Эндомедиум, ЭлМед), цены по запросу</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616450774</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0348100043326000102</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q27nr7kub1j7074</t>
+          <t>http://www.rts-tender.ru</t>
         </is>
       </c>
     </row>
@@ -1806,70 +1814,66 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 09:41</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>0348100043326000102</t>
+          <t>0325300007726000124</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Федеральное ГБУЗ «Медико-санитарная часть № 152 Федеральног…</t>
+          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Поставка медицинский изделий лот 2</t>
+          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной …</t>
+          <t>44-ФЗ · запрос котировок</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>1065306.62</v>
+        <v>496200</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>798980</v>
+        <v>300000</v>
       </c>
       <c r="J20" s="8" t="n">
+        <v>0.3954050785973398</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="K20" s="8" t="n">
-        <v>0.15</v>
-      </c>
       <c r="L20" s="7" t="n">
-        <v>62066</v>
+        <v>50413.31835616439</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>лапароскопический инструмент; нацрежим — российские (Эндомедиум, ЭлМед), цены по запросу</t>
-        </is>
-      </c>
+        <v>0.3704919206562006</v>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>перепроверено: цены 2026 по позициям</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0348100043326000102</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>http://www.rts-tender.ru</t>
+          <t>http://roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -1879,68 +1883,64 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>22.10.2026 08:00</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>0325300007726000124</t>
+          <t>10762184</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>ГБУЗ АО «Городская поликлиника №5», Астрахань</t>
+          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Пробирки вакуумные K3ЭДТА, 30 000 шт</t>
+          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>44-ФЗ · запрос котировок</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Росэлторг</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>496200</v>
+        <v>443486.33</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>300000</v>
+        <v>329310</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.3954050785973398</v>
+        <v>0.257</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>50413.31835616439</v>
+        <v>47437</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3704919206562006</v>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
-        <is>
-          <t>перепроверено: цены 2026 по позициям</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0325300007726000124</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr">
-        <is>
-          <t>http://roseltorg.ru</t>
-        </is>
-      </c>
+        <v>0.227</v>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>оценка (низкая)</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>малая закупка СИЗ — позиции неизвестны</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1948,51 +1948,51 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>22.10.2026 08:00</t>
+          <t>21.10.2026 13:00</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>10762184</t>
+          <t>588439</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
+          <t>ООО «Карсар»</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
+          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
+          <t>Коммерческие · Конкурентный лист с пере…</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Электронная торговая площадка ONLINECONTRACT</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>443486.33</v>
+        <v>203056.8</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>329310</v>
+        <v>129000</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.257</v>
+        <v>0.365</v>
       </c>
       <c r="K22" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>47437</v>
+        <v>40841</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.227</v>
+        <v>0.339</v>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>малая закупка СИЗ — позиции неизвестны</t>
+          <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
         </is>
       </c>
       <c r="P22" s="5" t="inlineStr"/>
@@ -2013,51 +2013,51 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>21.10.2026 13:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>588439</t>
+          <t>32616477523</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ООО «Карсар»</t>
+          <t>АО «Коми Тепловая Компания»</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертифи…</t>
+          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Коммерческие · Конкурентный лист с пере…</t>
+          <t>223-ФЗ · Закупка иного способа размещен…</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Электронная торговая площадка ONLINECONTRACT</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>203056.8</v>
+        <v>210371.75</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>129000</v>
+        <v>157779</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.365</v>
+        <v>0.25</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>40841</v>
+        <v>21126</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.339</v>
+        <v>0.2191</v>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
@@ -2066,151 +2066,86 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>образцы и сертификаты до 21.10 13:00; количество неизвестно</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
+          <t>видеонаблюдение — нужна спецификация</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>26.10.2026 10:00</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>32616477523</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>АО «Коми Тепловая Компания»</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>223-ФЗ · Закупка иного способа размещен…</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>РТС-тендер</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>210371.75</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>157779</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>21126</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>0.2191</v>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>оценка (низкая)</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>видеонаблюдение — нужна спецификация</t>
-        </is>
-      </c>
-      <c r="P24" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="12" t="inlineStr"/>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="12" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr"/>
+      <c r="B24" s="12" t="inlineStr"/>
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr"/>
-      <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr"/>
-      <c r="H25" s="13" t="n">
-        <v>125570195.97</v>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>64958953</v>
-      </c>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="13" t="n">
-        <v>31421756.62144464</v>
-      </c>
-      <c r="M25" s="14" t="n"/>
-      <c r="N25" s="14" t="n"/>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="n"/>
-      <c r="Q25" s="14" t="n"/>
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr"/>
+      <c r="G24" s="12" t="inlineStr"/>
+      <c r="H24" s="13" t="n">
+        <v>121400445.97</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>62033053</v>
+      </c>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="13" t="n">
+        <v>30826196.61815697</v>
+      </c>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/MARGIN30_2010.xlsx
+++ b/MARGIN30_2010.xlsx
@@ -694,19 +694,19 @@
         <v>101102908</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>49931509</v>
+        <v>54810725</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.506131821648493</v>
+        <v>0.4578719239213179</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>0.15</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>27230001.01395177</v>
+        <v>22809966.02655452</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.469413606444056</v>
+        <v>0.4175656716896615</v>
       </c>
       <c r="N4" s="9" t="inlineStr">
         <is>
@@ -2096,12 +2096,12 @@
         <v>121400445.97</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>62033053</v>
+        <v>66912269</v>
       </c>
       <c r="J24" s="14" t="n"/>
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="13" t="n">
-        <v>30826196.61815697</v>
+        <v>26406161.63075971</v>
       </c>
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
